--- a/output/pdf_financials_xlsx/HPS.A.xlsx
+++ b/output/pdf_financials_xlsx/HPS.A.xlsx
@@ -2328,7 +2328,7 @@
         <v>13.838</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>14.049</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>7.814</v>
@@ -2444,7 +2444,7 @@
         <v>13.838</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>14.049</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>7.814</v>
@@ -3140,7 +3140,7 @@
         <v>4.163</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>18.023</v>
+        <v>3.974</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>2.346</v>
@@ -24732,7 +24732,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -52535,7 +52535,7 @@
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -53882,7 +53882,7 @@
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -61952,7 +61952,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -62358,7 +62358,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -63053,7 +63053,7 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
@@ -64437,7 +64437,7 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -65635,7 +65635,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -67641,7 +67641,7 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E604" s="5" t="n">

--- a/output/pdf_financials_xlsx/HPS.A.xlsx
+++ b/output/pdf_financials_xlsx/HPS.A.xlsx
@@ -2043,16 +2043,16 @@
         <v>1.208</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>1.329</v>
+        <v>6.555</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.326</v>
+        <v>7.044</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.395</v>
+        <v>6.833</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>1.425</v>
+        <v>6.525</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>1.361</v>
@@ -2061,19 +2061,19 @@
         <v>1.097</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.471</v>
+        <v>7.563</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>3.785</v>
+        <v>76.405</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.3</v>
+        <v>121.1</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.441</v>
+        <v>131.379</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>1.656</v>
+        <v>135.27</v>
       </c>
     </row>
     <row r="29">
@@ -2101,16 +2101,16 @@
         <v>11.175</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>6.072</v>
+        <v>11.298</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.983</v>
+        <v>17.701</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7.851</v>
+        <v>13.289</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>17.428</v>
+        <v>22.528</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>12.014</v>
@@ -2119,19 +2119,19 @@
         <v>20.285</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>22.721</v>
+        <v>28.813</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>60.954</v>
+        <v>133.574</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>85.294</v>
+        <v>205.094</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>98.363</v>
+        <v>228.301</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>98.55200000000001</v>
+        <v>232.166</v>
       </c>
     </row>
     <row r="30">
@@ -2159,16 +2159,16 @@
         <v>4.599882275943542</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.450798366134423</v>
+        <v>4.560131742520868</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.363182213742403</v>
+        <v>6.445188046854235</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>2.857059677648266</v>
+        <v>4.836003828336239</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.122929365678852</v>
+        <v>7.914697770829307</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>3.825115734107654</v>
@@ -2177,19 +2177,19 @@
         <v>5.653851085060008</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>5.976033792562901</v>
+        <v>7.578339935087137</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>10.914579990832</v>
+        <v>23.91810394224158</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>12.01215665066811</v>
+        <v>28.88387525631492</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>12.47723063652739</v>
+        <v>28.95971281426796</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>10.97149473145154</v>
+        <v>25.84633539473757</v>
       </c>
     </row>
     <row r="31">
@@ -6175,55 +6175,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.782</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.208</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>6.555</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>7.044</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>6.833</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>6.525</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.361</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>7.563</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>76.405</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>121.1</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>131.379</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>135.27</v>
       </c>
     </row>
     <row r="101">
@@ -6877,7 +6877,7 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -6895,16 +6895,16 @@
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>1.583</v>
       </c>
       <c r="N112" s="3" t="n">
         <v>0</v>
@@ -30428,7 +30428,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -31004,7 +31004,11 @@
           <t>Depreciation of property, plant and equipment, total</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -34991,7 +34995,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -36686,7 +36690,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -38375,7 +38379,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -39505,7 +39513,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -39600,7 +39612,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -49108,7 +49120,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E415" s="5" t="n">

--- a/output/pdf_financials_xlsx/HPS.A.xlsx
+++ b/output/pdf_financials_xlsx/HPS.A.xlsx
@@ -977,49 +977,49 @@
         <v>49.856</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>47.967</v>
+        <v>13.642</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>53.991</v>
+        <v>13.039</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>64.788</v>
+        <v>18.18</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>60.601</v>
+        <v>11.036</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>57.485</v>
+        <v>6.46</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>65.88200000000001</v>
+        <v>12.644</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>66.91</v>
+        <v>10.873</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>72.992</v>
+        <v>16.884</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>72.935</v>
+        <v>13.779</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>87.959</v>
+        <v>20.543</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>102.431</v>
+        <v>23.151</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>165.185</v>
+        <v>59.441</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>231.011</v>
+        <v>86.721</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>258.278</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>272.319</v>
+        <v>104.019</v>
       </c>
     </row>
     <row r="12">
@@ -1765,10 +1765,10 @@
         <v>6.114</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.211</v>
+        <v>-12.917</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.485</v>
+        <v>11.607</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>15.176</v>
@@ -1939,10 +1939,10 @@
         <v>11.757692</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.191818</v>
+        <v>11.742727</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>0.489899</v>
+        <v>11.724242</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>11.85625</v>
@@ -2287,10 +2287,10 @@
         <v>2.148014123350958</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.06717990843155609</v>
+        <v>-4.112620271139384</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>0.1351795798005474</v>
+        <v>3.235112129371039</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>3.991562379998001</v>
@@ -2688,37 +2688,37 @@
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>4.868</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>4.287</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>4.024</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>4.934</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0</v>
+        <v>4.891</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>0</v>
+        <v>3.415</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>3.579</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>4.952</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>6.923</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>5.843</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="41">
@@ -2746,37 +2746,37 @@
         <v>49.302</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>47.381</v>
+        <v>52.249</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>61.951</v>
+        <v>66.238</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>49.969</v>
+        <v>53.993</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>59.17</v>
+        <v>64.104</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>69.01000000000001</v>
+        <v>73.901</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>64.004</v>
+        <v>67.419</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>72.004</v>
+        <v>75.583</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>86.70099999999999</v>
+        <v>91.65300000000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>128.03</v>
+        <v>134.953</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>140.4</v>
+        <v>146.243</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>168.074</v>
+        <v>173.574</v>
       </c>
     </row>
     <row r="42">
@@ -3152,37 +3152,37 @@
         <v>5.506</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>12.032</v>
+        <v>7.164</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.848</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.981</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.12</v>
+        <v>0.186</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.035</v>
+        <v>0.144</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.283</v>
+        <v>0.868</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.322</v>
+        <v>0.743</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>8.943</v>
+        <v>3.991</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>14.227</v>
+        <v>7.304</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>15.966</v>
+        <v>10.123</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>17.875</v>
+        <v>12.375</v>
       </c>
     </row>
     <row r="49">
@@ -6147,10 +6147,10 @@
         <v>6.114</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.211</v>
+        <v>-12.917</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.485</v>
+        <v>11.607</v>
       </c>
       <c r="N99" s="3" t="n">
         <v>15.176</v>
@@ -6523,16 +6523,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-17.107</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>11.18</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>-0.876</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-7.73</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>2.152</v>
@@ -6608,28 +6608,28 @@
         <v>0.171</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>2.183</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>19.954</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>17.092</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>0</v>
+        <v>8.778</v>
       </c>
     </row>
     <row r="108">
@@ -7103,55 +7103,55 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.042</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.207</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.182</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-1.084</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.893</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-1.472</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.172</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.163</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.466</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.323</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-1.016</v>
       </c>
       <c r="O116" s="3" t="n">
-        <v>0</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>0</v>
+        <v>-0.384</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="117">
@@ -7423,10 +7423,10 @@
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.053</v>
       </c>
       <c r="M121" s="3" t="n">
-        <v>0</v>
+        <v>-0.316</v>
       </c>
       <c r="N121" s="3" t="n">
         <v>0</v>
@@ -7906,13 +7906,13 @@
         <v>4.939</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>11.292</v>
+        <v>3.883</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>-10.191</v>
+        <v>-12.047</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>6.234</v>
+        <v>4.648</v>
       </c>
       <c r="J129" s="3" t="n">
         <v>-0.463</v>
@@ -7921,10 +7921,10 @@
         <v>-12.7</v>
       </c>
       <c r="L129" s="3" t="n">
-        <v>1.65</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>-7.016</v>
+        <v>-12.963</v>
       </c>
       <c r="N129" s="3" t="n">
         <v>-4.257</v>
@@ -8251,43 +8251,43 @@
         <v>2.709</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>17.324</v>
+        <v>21.879</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-2.922</v>
+        <v>4.487</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>14.157</v>
+        <v>16.013</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>14.103</v>
+        <v>15.689</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>13.052</v>
+        <v>20.74</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.287</v>
+        <v>5.413</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>4.586</v>
+        <v>6.925</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>14.128</v>
+        <v>20.075</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>15.396</v>
+        <v>21.779</v>
       </c>
       <c r="O135" s="3" t="n">
-        <v>28.367</v>
+        <v>44.435</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>23.939</v>
+        <v>47.923</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>24.118</v>
+        <v>51.215</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-8.608000000000001</v>
+        <v>34.005</v>
       </c>
     </row>
   </sheetData>
@@ -30909,7 +30909,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -31200,7 +31204,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -31901,7 +31909,11 @@
           <t>Acquisition of intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -33558,7 +33570,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -35492,7 +35508,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -35793,7 +35813,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -37585,7 +37609,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -37882,7 +37910,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -38751,7 +38783,11 @@
           <t>Share repurchase (note 17)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -40204,7 +40240,11 @@
           <t>Share repurchase (note 16)</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -41354,7 +41394,11 @@
           <t>Share-based compensation expense</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -41643,7 +41687,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -45302,7 +45350,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -46999,7 +47051,11 @@
           <t>Change in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -47805,7 +47861,11 @@
           <t>Change in non-cash operating working capital (Note 20)</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -49419,7 +49479,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E418" s="5" t="n">
         <v>-0.677</v>
       </c>
@@ -50025,7 +50089,11 @@
           <t>Change in non-cash operating working capital (Note 18)</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E424" s="5" t="n">
         <v>-17.107</v>
       </c>
@@ -51342,7 +51410,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E437" s="5" t="n">
         <v>-0.042</v>
       </c>
@@ -52470,7 +52542,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -55642,7 +55718,11 @@
           <t>Earnings from operations</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -56143,7 +56223,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
